--- a/storage/app/templates/plantilla_cronograma_mantenimiento_equipos.xlsx
+++ b/storage/app/templates/plantilla_cronograma_mantenimiento_equipos.xlsx
@@ -75,7 +75,7 @@
   </si>
   <si>
     <t xml:space="preserve"> PARA CUMPLIMIENTO
-    01 PENDIENTE
+    01 PROXIMOS A VENCERSE
     02 NUEVO NO APLICA
     03 REALIZADO</t>
   </si>
